--- a/artfynd/A 23498-2024 artfynd.xlsx
+++ b/artfynd/A 23498-2024 artfynd.xlsx
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119694496</v>
+        <v>119694472</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,30 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1101,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119694472</v>
+        <v>119694496</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,31 +1114,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 23498-2024 artfynd.xlsx
+++ b/artfynd/A 23498-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119694456</v>
+        <v>119694491</v>
       </c>
       <c r="B3" t="n">
-        <v>90971</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536526</v>
+        <v>536492</v>
       </c>
       <c r="R3" t="n">
-        <v>6675093</v>
+        <v>6675096</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119694491</v>
+        <v>119694456</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>90971</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +905,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536492</v>
+        <v>536526</v>
       </c>
       <c r="R4" t="n">
-        <v>6675096</v>
+        <v>6675093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119694472</v>
+        <v>119694496</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,31 +1007,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119694496</v>
+        <v>119694472</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,30 +1113,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 23498-2024 artfynd.xlsx
+++ b/artfynd/A 23498-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119694491</v>
+        <v>119694496</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,28 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -995,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119694496</v>
+        <v>119694491</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,26 +1009,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 23498-2024 artfynd.xlsx
+++ b/artfynd/A 23498-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119694518</v>
+        <v>119694456</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536397</v>
+        <v>536526</v>
       </c>
       <c r="R2" t="n">
-        <v>6675133</v>
+        <v>6675093</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -784,12 +779,7 @@
         <v>119694496</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119694456</v>
+        <v>119694404</v>
       </c>
       <c r="B4" t="n">
-        <v>90971</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536526</v>
+        <v>536527</v>
       </c>
       <c r="R4" t="n">
-        <v>6675093</v>
+        <v>6675001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,44 +978,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119694491</v>
+        <v>119694518</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536492</v>
+        <v>536397</v>
       </c>
       <c r="R5" t="n">
-        <v>6675096</v>
+        <v>6675133</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,43 +1079,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119694472</v>
+        <v>119694491</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,6 +1179,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119694472</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arvlingudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>536492</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6675096</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23498-2024 artfynd.xlsx
+++ b/artfynd/A 23498-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694456</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694518</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,8 +1311,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>